--- a/api/src/main/resources/importaciones/Productos.xlsx
+++ b/api/src/main/resources/importaciones/Productos.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20417"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9911CA37-A918-40AE-8783-C0E1709DB355}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEBD6C93-823D-40E5-B78F-17FE135C1DC8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="93">
   <si>
     <t>Código del artículo</t>
   </si>
@@ -49,9 +49,6 @@
     <t>Categoría</t>
   </si>
   <si>
-    <t>GRUPO 1</t>
-  </si>
-  <si>
     <t>UND</t>
   </si>
   <si>
@@ -112,21 +109,6 @@
     <t>6 cm</t>
   </si>
   <si>
-    <t>Samsung</t>
-  </si>
-  <si>
-    <t>Apple</t>
-  </si>
-  <si>
-    <t>HP</t>
-  </si>
-  <si>
-    <t>Panosonic</t>
-  </si>
-  <si>
-    <t>Tecnologia</t>
-  </si>
-  <si>
     <t>RC!d3000</t>
   </si>
   <si>
@@ -305,6 +287,15 @@
   </si>
   <si>
     <t>1700519</t>
+  </si>
+  <si>
+    <t>Grupo1</t>
+  </si>
+  <si>
+    <t>LCD</t>
+  </si>
+  <si>
+    <t>Categoria 1</t>
   </si>
 </sst>
 </file>
@@ -346,10 +337,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -368,9 +360,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -408,9 +400,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -443,9 +435,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -478,9 +487,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -654,8 +680,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P21"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:P22"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="19.28515625" customWidth="1"/>
     <col min="3" max="3" width="31.42578125" customWidth="1"/>
@@ -698,16 +724,16 @@
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B2" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -716,48 +742,48 @@
         <v>2</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H2" t="s">
-        <v>31</v>
+        <v>91</v>
       </c>
       <c r="I2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J2" t="s">
-        <v>35</v>
+        <v>92</v>
       </c>
       <c r="K2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L2" t="s">
         <v>12</v>
       </c>
-      <c r="L2" t="s">
-        <v>13</v>
-      </c>
       <c r="M2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N2" t="s">
         <v>14</v>
       </c>
-      <c r="N2" t="s">
-        <v>15</v>
-      </c>
       <c r="O2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P2" t="s">
         <v>16</v>
-      </c>
-      <c r="P2" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="B3" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="D3" t="s">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -766,48 +792,48 @@
         <v>2</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H3" t="s">
-        <v>32</v>
+        <v>91</v>
       </c>
       <c r="I3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J3" t="s">
-        <v>35</v>
+        <v>92</v>
       </c>
       <c r="K3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M3" t="s">
+        <v>13</v>
+      </c>
+      <c r="N3" t="s">
         <v>18</v>
       </c>
-      <c r="M3" t="s">
-        <v>14</v>
-      </c>
-      <c r="N3" t="s">
+      <c r="O3" t="s">
+        <v>15</v>
+      </c>
+      <c r="P3" t="s">
         <v>19</v>
-      </c>
-      <c r="O3" t="s">
-        <v>16</v>
-      </c>
-      <c r="P3" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="B4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="D4" t="s">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -816,48 +842,48 @@
         <v>2</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H4" t="s">
-        <v>33</v>
+        <v>91</v>
       </c>
       <c r="I4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J4" t="s">
-        <v>35</v>
+        <v>92</v>
       </c>
       <c r="K4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L4" t="s">
+        <v>20</v>
+      </c>
+      <c r="M4" t="s">
+        <v>13</v>
+      </c>
+      <c r="N4" t="s">
         <v>21</v>
       </c>
-      <c r="M4" t="s">
-        <v>14</v>
-      </c>
-      <c r="N4" t="s">
+      <c r="O4" t="s">
+        <v>15</v>
+      </c>
+      <c r="P4" t="s">
         <v>22</v>
-      </c>
-      <c r="O4" t="s">
-        <v>16</v>
-      </c>
-      <c r="P4" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="B5" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="D5" t="s">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -866,48 +892,48 @@
         <v>2</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H5" t="s">
-        <v>34</v>
+        <v>91</v>
       </c>
       <c r="I5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J5" t="s">
-        <v>35</v>
+        <v>92</v>
       </c>
       <c r="K5" t="s">
+        <v>11</v>
+      </c>
+      <c r="L5" t="s">
         <v>12</v>
       </c>
-      <c r="L5" t="s">
-        <v>13</v>
-      </c>
       <c r="M5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N5" t="s">
+        <v>23</v>
+      </c>
+      <c r="O5" t="s">
+        <v>15</v>
+      </c>
+      <c r="P5" t="s">
         <v>24</v>
-      </c>
-      <c r="O5" t="s">
-        <v>16</v>
-      </c>
-      <c r="P5" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="B6" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -916,48 +942,48 @@
         <v>2</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H6" t="s">
-        <v>31</v>
+        <v>91</v>
       </c>
       <c r="I6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J6" t="s">
-        <v>35</v>
+        <v>92</v>
       </c>
       <c r="K6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N6" t="s">
+        <v>25</v>
+      </c>
+      <c r="O6" t="s">
+        <v>15</v>
+      </c>
+      <c r="P6" t="s">
         <v>26</v>
-      </c>
-      <c r="O6" t="s">
-        <v>16</v>
-      </c>
-      <c r="P6" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="B7" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D7" t="s">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -966,48 +992,48 @@
         <v>2</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H7" t="s">
-        <v>32</v>
+        <v>91</v>
       </c>
       <c r="I7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J7" t="s">
-        <v>35</v>
+        <v>92</v>
       </c>
       <c r="K7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M7" t="s">
+        <v>13</v>
+      </c>
+      <c r="N7" t="s">
         <v>14</v>
       </c>
-      <c r="N7" t="s">
-        <v>15</v>
-      </c>
       <c r="O7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="B8" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D8" t="s">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -1016,48 +1042,48 @@
         <v>2</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H8" t="s">
-        <v>33</v>
+        <v>91</v>
       </c>
       <c r="I8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J8" t="s">
-        <v>35</v>
+        <v>92</v>
       </c>
       <c r="K8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="M8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O8" t="s">
+        <v>15</v>
+      </c>
+      <c r="P8" t="s">
         <v>16</v>
-      </c>
-      <c r="P8" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="B9" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="D9" t="s">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -1066,98 +1092,53 @@
         <v>2</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H9" t="s">
-        <v>34</v>
+        <v>91</v>
       </c>
       <c r="I9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J9" t="s">
-        <v>35</v>
+        <v>92</v>
       </c>
       <c r="K9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B10" t="s">
-        <v>44</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E10">
-        <v>1</v>
-      </c>
-      <c r="F10">
-        <v>2</v>
-      </c>
-      <c r="G10">
-        <v>2</v>
-      </c>
-      <c r="H10" t="s">
-        <v>31</v>
-      </c>
-      <c r="I10" t="s">
-        <v>11</v>
-      </c>
-      <c r="J10" t="s">
-        <v>35</v>
-      </c>
-      <c r="K10" t="s">
-        <v>12</v>
-      </c>
-      <c r="L10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M10" t="s">
-        <v>14</v>
-      </c>
-      <c r="N10" t="s">
-        <v>24</v>
-      </c>
-      <c r="O10" t="s">
-        <v>16</v>
-      </c>
-      <c r="P10" t="s">
-        <v>23</v>
-      </c>
+      <c r="A10" s="1"/>
+      <c r="C10" s="2"/>
+      <c r="F10"/>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="B11" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="D11" t="s">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -1166,48 +1147,48 @@
         <v>2</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H11" t="s">
-        <v>32</v>
+        <v>91</v>
       </c>
       <c r="I11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J11" t="s">
-        <v>35</v>
+        <v>92</v>
       </c>
       <c r="K11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L11" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="M11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N11" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="O11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P11" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="B12" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="D12" t="s">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -1216,48 +1197,48 @@
         <v>2</v>
       </c>
       <c r="G12">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H12" t="s">
-        <v>33</v>
+        <v>91</v>
       </c>
       <c r="I12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J12" t="s">
-        <v>35</v>
+        <v>92</v>
       </c>
       <c r="K12" t="s">
+        <v>11</v>
+      </c>
+      <c r="L12" t="s">
         <v>12</v>
       </c>
-      <c r="L12" t="s">
-        <v>18</v>
-      </c>
       <c r="M12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N12" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="O12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P12" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B13" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="D13" t="s">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -1266,48 +1247,48 @@
         <v>2</v>
       </c>
       <c r="G13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H13" t="s">
-        <v>34</v>
+        <v>91</v>
       </c>
       <c r="I13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J13" t="s">
-        <v>35</v>
+        <v>92</v>
       </c>
       <c r="K13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L13" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="M13" t="s">
+        <v>13</v>
+      </c>
+      <c r="N13" t="s">
         <v>14</v>
       </c>
-      <c r="N13" t="s">
-        <v>19</v>
-      </c>
       <c r="O13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P13" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="B14" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D14" t="s">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -1316,48 +1297,48 @@
         <v>2</v>
       </c>
       <c r="G14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H14" t="s">
-        <v>31</v>
+        <v>91</v>
       </c>
       <c r="I14" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J14" t="s">
-        <v>35</v>
+        <v>92</v>
       </c>
       <c r="K14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L14" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="M14" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N14" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="O14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P14" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="B15" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D15" t="s">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -1366,48 +1347,48 @@
         <v>2</v>
       </c>
       <c r="G15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H15" t="s">
-        <v>32</v>
+        <v>91</v>
       </c>
       <c r="I15" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J15" t="s">
-        <v>35</v>
+        <v>92</v>
       </c>
       <c r="K15" t="s">
+        <v>11</v>
+      </c>
+      <c r="L15" t="s">
         <v>12</v>
       </c>
-      <c r="L15" t="s">
-        <v>18</v>
-      </c>
       <c r="M15" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N15" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="O15" t="s">
+        <v>15</v>
+      </c>
+      <c r="P15" t="s">
         <v>16</v>
-      </c>
-      <c r="P15" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="B16" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="s">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="E16">
         <v>1</v>
@@ -1416,48 +1397,48 @@
         <v>2</v>
       </c>
       <c r="G16">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H16" t="s">
-        <v>33</v>
+        <v>91</v>
       </c>
       <c r="I16" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J16" t="s">
-        <v>35</v>
+        <v>92</v>
       </c>
       <c r="K16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L16" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="M16" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N16" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="O16" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P16" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="B17" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D17" t="s">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -1466,48 +1447,48 @@
         <v>2</v>
       </c>
       <c r="G17">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H17" t="s">
-        <v>34</v>
+        <v>91</v>
       </c>
       <c r="I17" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J17" t="s">
-        <v>35</v>
+        <v>92</v>
       </c>
       <c r="K17" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L17" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="M17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N17" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="O17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P17" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="B18" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="D18" t="s">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -1516,48 +1497,48 @@
         <v>2</v>
       </c>
       <c r="G18">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H18" t="s">
-        <v>31</v>
+        <v>91</v>
       </c>
       <c r="I18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J18" t="s">
-        <v>35</v>
+        <v>92</v>
       </c>
       <c r="K18" t="s">
+        <v>11</v>
+      </c>
+      <c r="L18" t="s">
         <v>12</v>
       </c>
-      <c r="L18" t="s">
-        <v>18</v>
-      </c>
       <c r="M18" t="s">
+        <v>13</v>
+      </c>
+      <c r="N18" t="s">
         <v>14</v>
       </c>
-      <c r="N18" t="s">
-        <v>19</v>
-      </c>
       <c r="O18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P18" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="B19" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="D19" t="s">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="E19">
         <v>1</v>
@@ -1566,48 +1547,48 @@
         <v>2</v>
       </c>
       <c r="G19">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H19" t="s">
-        <v>32</v>
+        <v>91</v>
       </c>
       <c r="I19" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J19" t="s">
-        <v>35</v>
+        <v>92</v>
       </c>
       <c r="K19" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L19" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="M19" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N19" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="O19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P19" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="B20" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="D20" t="s">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="E20">
         <v>1</v>
@@ -1616,48 +1597,48 @@
         <v>2</v>
       </c>
       <c r="G20">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H20" t="s">
-        <v>33</v>
+        <v>91</v>
       </c>
       <c r="I20" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J20" t="s">
-        <v>35</v>
+        <v>92</v>
       </c>
       <c r="K20" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L20" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="M20" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N20" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="O20" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P20" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="B21" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="D21" t="s">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="E21">
         <v>1</v>
@@ -1666,34 +1647,84 @@
         <v>2</v>
       </c>
       <c r="G21">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H21" t="s">
-        <v>34</v>
+        <v>91</v>
       </c>
       <c r="I21" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J21" t="s">
-        <v>35</v>
+        <v>92</v>
       </c>
       <c r="K21" t="s">
+        <v>11</v>
+      </c>
+      <c r="L21" t="s">
         <v>12</v>
       </c>
-      <c r="L21" t="s">
-        <v>18</v>
-      </c>
       <c r="M21" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N21" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="O21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P21" t="s">
-        <v>23</v>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B22" t="s">
+        <v>49</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D22" t="s">
+        <v>90</v>
+      </c>
+      <c r="E22">
+        <v>1</v>
+      </c>
+      <c r="F22">
+        <v>2</v>
+      </c>
+      <c r="G22">
+        <v>4</v>
+      </c>
+      <c r="H22" t="s">
+        <v>91</v>
+      </c>
+      <c r="I22" t="s">
+        <v>10</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="K22" t="s">
+        <v>11</v>
+      </c>
+      <c r="L22" t="s">
+        <v>17</v>
+      </c>
+      <c r="M22" t="s">
+        <v>13</v>
+      </c>
+      <c r="N22" t="s">
+        <v>25</v>
+      </c>
+      <c r="O22" t="s">
+        <v>15</v>
+      </c>
+      <c r="P22" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -1706,7 +1737,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>
@@ -1716,7 +1747,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>
